--- a/TBIM_Interactive_Map_Database_Template.xlsx
+++ b/TBIM_Interactive_Map_Database_Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bimsurf.sharepoint.com/sites/BIMSurf/Shared Documents/General/01_Document/TBIM/BIM BOOT CAMP 2026/TBIM_Interactive_Map/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{EE77D508-D276-4B7F-BB86-60814C83D91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB56B7BD-2701-4573-9255-7B906B56BB30}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{EE77D508-D276-4B7F-BB86-60814C83D91B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B29E799A-5DED-A147-8727-EB6BD5D55052}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01_Architecture" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="660" uniqueCount="427">
   <si>
     <t>TBIM BIM Bootcamp 2026 – Interactive Event Map Architecture</t>
   </si>
@@ -200,9 +200,6 @@
     <t>1F</t>
   </si>
   <si>
-    <t>Need detail</t>
-  </si>
-  <si>
     <t>J2</t>
   </si>
   <si>
@@ -308,27 +305,15 @@
     <t>Facility</t>
   </si>
   <si>
-    <t>Registration desk; 2 staff standby. T-shirt distribution after registration.</t>
-  </si>
-  <si>
     <t>Ready</t>
   </si>
   <si>
-    <t>2 desks / 4 seats</t>
-  </si>
-  <si>
     <t>ADV</t>
   </si>
   <si>
-    <t>ADVICE</t>
-  </si>
-  <si>
     <t>Advice</t>
   </si>
   <si>
-    <t>Advice zone 2.5x2m</t>
-  </si>
-  <si>
     <t>ENT</t>
   </si>
   <si>
@@ -336,12 +321,6 @@
   </si>
   <si>
     <t>Entrance</t>
-  </si>
-  <si>
-    <t>Main entrance to the event floor.</t>
-  </si>
-  <si>
-    <t>Future: link directions to training rooms</t>
   </si>
   <si>
     <t>RoomID</t>
@@ -983,22 +962,367 @@
     <t>Executive Panel Discussion</t>
   </si>
   <si>
-    <t>Hardware Booth</t>
-  </si>
-  <si>
     <t>14F</t>
   </si>
   <si>
     <t>2F</t>
+  </si>
+  <si>
+    <t>Rot_deg</t>
+  </si>
+  <si>
+    <t>Hardware Zone (ADVICE)</t>
+  </si>
+  <si>
+    <t>YBIM</t>
+  </si>
+  <si>
+    <t>Young BIM</t>
+  </si>
+  <si>
+    <t>BRK</t>
+  </si>
+  <si>
+    <t>Break</t>
+  </si>
+  <si>
+    <t>ผู้รับเหมาก่อสร้างและออกแบบครบวงจรในประเทศไทย พร้อมโอกาสร่วมงานด้านวิศวกรรมและการบริหารโครงการ / An integrated design-and-construction company in Thailand with career opportunities in engineering and project delivery.</t>
+  </si>
+  <si>
+    <t>งานก่อสร้างอาคารและโยธา, ออกแบบและก่อสร้าง, โอกาสงานวิศวกร / Building and civil construction, design-build services, engineering careers.</t>
+  </si>
+  <si>
+    <t>General Enquiries: contact@thaiobayashi.co.th</t>
+  </si>
+  <si>
+    <t>02-252-5200</t>
+  </si>
+  <si>
+    <t>https://www.thaiobayashi.co.th/</t>
+  </si>
+  <si>
+    <t>Official company contact and career pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>บริษัทก่อสร้างชั้นนำ ให้บริการตั้งแต่งานออกแบบจนถึงงานก่อสร้าง และเปิดรับบุคลากรสาย BIM/วิศวกรรม / A leading contractor providing design-to-construction services and recruiting BIM and engineering talent.</t>
+  </si>
+  <si>
+    <t>ออกแบบและก่อสร้าง, อาคารและอุตสาหกรรม, งานโครงสร้างเหล็ก, BIM management / Design and construction, buildings and industrial works, structural steel, BIM management.</t>
+  </si>
+  <si>
+    <t>HR Department</t>
+  </si>
+  <si>
+    <t>02-338-8002 / 8009</t>
+  </si>
+  <si>
+    <t>https://cn-thai.co.th/en/index.php/careers/</t>
+  </si>
+  <si>
+    <t>Official careers and contact pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>กลุ่มธุรกิจวิศวกรรมและก่อสร้างที่ดำเนินงานโครงการภาครัฐและเอกชน พร้อมโอกาสสายงานก่อสร้างและโครงสร้างพื้นฐาน / An engineering and construction group delivering public- and private-sector projects, with careers across construction and infrastructure.</t>
+  </si>
+  <si>
+    <t>วิศวกรรมและก่อสร้าง, สาธารณูปโภคและพลังงาน, โครงสร้างพื้นฐานดิจิทัล, โลจิสติกส์ / Engineering and construction, utilities and power, digital infrastructure, logistics.</t>
+  </si>
+  <si>
+    <t>Recruitment: recruit@stecongroup.co.th</t>
+  </si>
+  <si>
+    <t>02-610-4900</t>
+  </si>
+  <si>
+    <t>https://www.stecongroup.co.th/en/home</t>
+  </si>
+  <si>
+    <t>Official Stecon Group pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>ผู้รับเหมาก่อสร้างไทยที่เน้นคุณภาพ เวลา ต้นทุน ความปลอดภัย และความรับผิดชอบต่อสังคม พร้อมรับบุคลากรสายโครงการ / A Thai contractor focused on quality, time, cost, safety and social responsibility, recruiting project professionals.</t>
+  </si>
+  <si>
+    <t>งานก่อสร้างอาคารและโครงการ, บริหารงานก่อสร้าง, โอกาสงานด้านวิศวกรรมและสนับสนุนโครงการ / Building and project construction, construction management, engineering and project-support careers.</t>
+  </si>
+  <si>
+    <t>Human Resources: personnel@synteccon.com</t>
+  </si>
+  <si>
+    <t>02-026-2288 ext. 1701</t>
+  </si>
+  <si>
+    <t>https://www.synteccon.com/en/career/</t>
+  </si>
+  <si>
+    <t>Official career and contact pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>แพลตฟอร์มคอนเทนต์และชุมชนสำหรับ BIM และ Digital Construction เชื่อมโยงนักออกแบบ วิศวกร ผู้รับเหมา และผู้ผลิตวัสดุ / A BIM and Digital Construction content platform and community connecting designers, engineers, contractors and product brands.</t>
+  </si>
+  <si>
+    <t>คอนเทนต์ BIM, ไลบรารี BIM object, บทความและบทเรียน, ความร่วมมือกับแบรนด์วัสดุก่อสร้าง / BIM content, BIM-object libraries, articles and tutorials, building-product brand partnerships.</t>
+  </si>
+  <si>
+    <t>BIMobject Thailand: contactth@bimobject.com</t>
+  </si>
+  <si>
+    <t>065-732-0243</t>
+  </si>
+  <si>
+    <t>https://bimspaces.com/</t>
+  </si>
+  <si>
+    <t>Official BIMSpaces pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>ผู้เชี่ยวชาญวัสดุทดแทนธรรมชาติ พร้อมบริการให้คำปรึกษา ออกแบบ ติดตั้ง และบริการหลังการขาย / A specialist in nature-inspired substitute materials with consultation, design, installation and after-sales service.</t>
+  </si>
+  <si>
+    <t>ไม้เทียม/WPC, อลูมิเนียมลายไม้, หินสังเคราะห์, กรีนวอลล์, วัสดุตกแต่ง / WPC and synthetic wood, wood-finish aluminium, artificial stone, green walls and decorative materials.</t>
+  </si>
+  <si>
+    <t>General Enquiries: info@solumat.co.th</t>
+  </si>
+  <si>
+    <t>02-726-6840 / 063-926-6226</t>
+  </si>
+  <si>
+    <t>https://solumat.co.th/</t>
+  </si>
+  <si>
+    <t>Official Solumat contact and catalogue pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>บูทร่วมของ Innoplan, JAI Group และ Wisdom—รอยืนยันชื่อนิติบุคคลและขอบเขตการนำเสนอจากผู้จัดงาน / Joint booth for Innoplan, JAI Group and Wisdom—legal entities and showcase scope require organizer confirmation.</t>
+  </si>
+  <si>
+    <t>คาดว่าเกี่ยวข้องกับงานออกแบบ สถาปัตยกรรม BIM และที่ปรึกษาโครงการ; โปรดยืนยันก่อนเผยแพร่ / Expected to cover design, architecture, BIM and project consultancy; confirm before publishing.</t>
+  </si>
+  <si>
+    <t>Organizer confirmation required</t>
+  </si>
+  <si>
+    <t>Needs confirmation</t>
+  </si>
+  <si>
+    <t>Please confirm the exact legal names, official websites, booth contact, and what each of the three partners will present.</t>
+  </si>
+  <si>
+    <t>บริษัทวิศวกรรมและก่อสร้างไทย ให้บริการตั้งแต่งานออกแบบจนส่งมอบ พร้อมใช้ BIM ในกระบวนการโครงการ / A Thai engineering and construction company delivering projects from design through handover, with BIM in its project workflow.</t>
+  </si>
+  <si>
+    <t>ออกแบบและวิศวกรรม, BIM, ประเมินราคา, บริหารงานก่อสร้าง, อาคาร โรงงาน โรงพยาบาล โรงแรม และดาต้าเซ็นเตอร์ / Design and engineering, BIM, commercial services, construction management, buildings, factories, hospitals, hotels and data centers.</t>
+  </si>
+  <si>
+    <t>General Enquiries: info@ritta.co.th</t>
+  </si>
+  <si>
+    <t>02-326-5000 / 02-105-5000</t>
+  </si>
+  <si>
+    <t>https://www.ritta.co.th/</t>
+  </si>
+  <si>
+    <t>Official Ritta company, solutions and contact pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>แบรนด์สีและโซลูชันปกป้องพื้นผิว—รอยืนยันว่าเป็น Berger Paints หรือ Beger Thailand ก่อนเผยแพร่ / Paint and surface-protection brand—confirm whether this is Berger Paints or Beger Thailand before publishing.</t>
+  </si>
+  <si>
+    <t>สีทาภายในและภายนอก, สารกันซึม, สีเคลือบและงานปกป้องพื้นผิว / Interior and exterior paints, waterproofing, coatings and surface protection.</t>
+  </si>
+  <si>
+    <t>Workbook says 'Berger' but Thailand search strongly surfaces 'Beger'. Please confirm the exact exhibitor spelling and official Thailand contact.</t>
+  </si>
+  <si>
+    <t>ผู้เชี่ยวชาญเทคโนโลยี 3D และ Immersive สำหรับงานออกแบบ วิศวกรรม ก่อสร้าง และการฝึกอบรม / A 3D and immersive-technology specialist for design, engineering, construction and training.</t>
+  </si>
+  <si>
+    <t>3D laser scanning, point clouds, AR/VR/MR, digital twin, Autodesk design solutions, consulting and training / สแกนเลเซอร์ 3 มิติ, พอยต์คลาวด์, AR/VR/MR, ดิจิทัลทวิน, Autodesk, ที่ปรึกษาและอบรม.</t>
+  </si>
+  <si>
+    <t>General Enquiries: info@sustain-solution.com</t>
+  </si>
+  <si>
+    <t>081-487-3005</t>
+  </si>
+  <si>
+    <t>https://www.sustain.co.th/</t>
+  </si>
+  <si>
+    <t>Official Sustainable Solution pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>เทคโนโลยีคอมพิวเตอร์สำหรับงานออกแบบ วิศวกรรม และการทำงานร่วมกัน ตั้งแต่เวิร์กสเตชันถึงโครงสร้างพื้นฐานข้อมูล / Computing technology for design, engineering and collaboration, from workstations to data infrastructure.</t>
+  </si>
+  <si>
+    <t>Precision workstations, laptops, monitors, servers, storage, data-center and support solutions / เวิร์กสเตชัน Precision, โน้ตบุ๊ก, จอภาพ, เซิร์ฟเวอร์, สตอเรจ, ดาต้าเซ็นเตอร์และบริการสนับสนุน.</t>
+  </si>
+  <si>
+    <t>Dell Thailand Sales / Support</t>
+  </si>
+  <si>
+    <t>https://www.dell.com/th-th/</t>
+  </si>
+  <si>
+    <t>Official Dell Thailand contact portal and company profile checked Sep 2026; use website for current sales channel.</t>
+  </si>
+  <si>
+    <t>ผู้จัดจำหน่ายสินค้าไอทีและการสื่อสารชั้นนำของไทย เชื่อมโยงฮาร์ดแวร์ ซอฟต์แวร์ และโซลูชันองค์กรจากแบรนด์ระดับโลก / A leading Thai ICT distributor connecting enterprise hardware, software and solutions from global brands.</t>
+  </si>
+  <si>
+    <t>คอมพิวเตอร์และอุปกรณ์ต่อพ่วง, ซอฟต์แวร์, ระบบไอทีองค์กร, อุปกรณ์สื่อสาร, ช่องทางตัวแทนและบริการหลังการขาย / Computers, peripherals, software, enterprise IT systems, communications, channel and after-sales services.</t>
+  </si>
+  <si>
+    <t>General Enquiries</t>
+  </si>
+  <si>
+    <t>02-553-8899</t>
+  </si>
+  <si>
+    <t>https://www.synnex.co.th/</t>
+  </si>
+  <si>
+    <t>Official Synnex Group profile checked Sep 2026; public switchboard cross-checked in business listing.</t>
+  </si>
+  <si>
+    <t>ผู้พัฒนาซอฟต์แวร์สำหรับงานออกแบบ วิศวกรรม ก่อสร้าง และบริหารวงจรชีวิตสินทรัพย์ด้วย BIM และระบบคลาวด์ / Software for design, engineering, construction and asset lifecycle workflows using BIM and cloud collaboration.</t>
+  </si>
+  <si>
+    <t>Revit, AutoCAD, Civil 3D, Navisworks, Autodesk Construction Cloud, Forma และ AEC Collection / Revit, AutoCAD, Civil 3D, Navisworks, Autodesk Construction Cloud, Forma and the AEC Collection.</t>
+  </si>
+  <si>
+    <t>Autodesk Sales / Support</t>
+  </si>
+  <si>
+    <t>https://www.autodesk.com/asean</t>
+  </si>
+  <si>
+    <t>Official Autodesk ASEAN product page checked Sep 2026; use website assistant or authorized partner for Thailand contact.</t>
+  </si>
+  <si>
+    <t>ผู้ให้บริการโซลูชันซอฟต์แวร์สำหรับ AEC และ Manufacturing และ Autodesk Partner ที่ให้บริการ BIM แบบครบวงจร / An AEC and manufacturing software-solutions provider and Autodesk Partner delivering end-to-end BIM services.</t>
+  </si>
+  <si>
+    <t>ซอฟต์แวร์ Autodesk, BIM assessment, training, pilot projects, consulting, implementation, modelling outsourcing and support / Autodesk software, BIM assessment, training, pilots, consulting, implementation, modelling outsourcing and support.</t>
+  </si>
+  <si>
+    <t>Sales: sales@synergysoft.co.th</t>
+  </si>
+  <si>
+    <t>02-692-2575 / 085-323-5453</t>
+  </si>
+  <si>
+    <t>https://synergysoft.co.th/</t>
+  </si>
+  <si>
+    <t>Official SynergySoft and Autodesk Partner pages checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>ผู้ให้บริการซอฟต์แวร์ออกแบบสำหรับอุตสาหกรรมสถาปัตยกรรมและก่อสร้าง โดยมี SketchUp เป็นผลิตภัณฑ์เด่น / A design-software provider for architecture and construction, prominently featuring SketchUp.</t>
+  </si>
+  <si>
+    <t>SketchUp และซอฟต์แวร์ออกแบบ/สร้างโมเดล 3 มิติสำหรับงาน AEC พร้อมการสนับสนุนด้านผลิตภัณฑ์ / SketchUp and 3D design/modelling software for AEC, with product support.</t>
+  </si>
+  <si>
+    <t>Product Enquiries</t>
+  </si>
+  <si>
+    <t>https://www.digitechone.co.th/</t>
+  </si>
+  <si>
+    <t>Official company site and Architect Expo exhibitor profile checked Sep 2026; public phone not confirmed.</t>
+  </si>
+  <si>
+    <t>องค์กรด้านมาตรฐานและการรับรองที่ช่วยยกระดับการบริหารข้อมูล BIM ตาม ISO 19650 สำหรับองค์กรและโครงการ / A standards and certification organization supporting ISO 19650 BIM information-management capability for organizations and projects.</t>
+  </si>
+  <si>
+    <t>หลักสูตร BIM/ISO 19650, การรับรองคุณวุฒิ, การฝึกอบรมแบบสด ออนไลน์ และ eLearning / BIM and ISO 19650 courses, qualifications, live training, online learning and eLearning.</t>
+  </si>
+  <si>
+    <t>Training Adviser</t>
+  </si>
+  <si>
+    <t>02-026-5297</t>
+  </si>
+  <si>
+    <t>https://www.bsigroup.com/th-TH/products-and-services/training-courses-and-qualifications/iso-19650-and-bim-training-online-courses/</t>
+  </si>
+  <si>
+    <t>Official BSI Thailand BIM training page checked Sep 2026.</t>
+  </si>
+  <si>
+    <t>จุดลงทะเบียน รับข้อมูลหน้างาน และรับเสื้อหลังลงทะเบียน โดยมีเจ้าหน้าที่ 2 คนประจำจุด / Event check-in, on-site information and T-shirt collection after registration, staffed by two team members.</t>
+  </si>
+  <si>
+    <t>ตรวจสอบรายชื่อและสถานะลงทะเบียน, แจกเอกสาร/เสื้อ, แนะนำโซนกิจกรรม / Registration verification, badge or material distribution, T-shirt collection and event directions.</t>
+  </si>
+  <si>
+    <t>Event Registration Team</t>
+  </si>
+  <si>
+    <t>2 desks / 4 seats | Event-operational copy; confirm any required ID, QR code or ticket before publishing.</t>
+  </si>
+  <si>
+    <t>โซนฮาร์ดแวร์โดย ADVICE สำหรับทดลองและปรึกษาอุปกรณ์คอมพิวเตอร์ที่เหมาะกับงาน BIM และงานออกแบบ / Hardware zone by ADVICE for exploring computers and peripherals suited to BIM and design workflows.</t>
+  </si>
+  <si>
+    <t>คอมพิวเตอร์ประกอบ, โน้ตบุ๊ก, เดสก์ท็อป, อุปกรณ์ต่อพ่วง และบริการหลังการขาย / Custom-built PCs, notebooks, desktops, peripherals and after-sales service.</t>
+  </si>
+  <si>
+    <t>ADVICE Customer Service</t>
+  </si>
+  <si>
+    <t>02-908-8888</t>
+  </si>
+  <si>
+    <t>https://www.advice.co.th/</t>
+  </si>
+  <si>
+    <t>Advice zone 2.5x2m | Official ADVICE company-information page checked Sep 2026; event display models should be confirmed with the booth team.</t>
+  </si>
+  <si>
+    <t>ทางเข้าหลักสู่พื้นที่จัดงานและจุดเริ่มต้นสำหรับค้นหาบูท ห้องอบรม และบริการต่าง ๆ / Main entrance to the event floor and the starting point for booths, training rooms and visitor services.</t>
+  </si>
+  <si>
+    <t>ป้ายต้อนรับ, แผนผังงาน, เส้นทางไปจุดลงทะเบียนและห้องอบรม / Welcome signage, event map, directions to registration and training rooms.</t>
+  </si>
+  <si>
+    <t>Event Information Team</t>
+  </si>
+  <si>
+    <t>Future: link directions to training rooms | Event-operational copy; add building access and lift directions when confirmed.</t>
+  </si>
+  <si>
+    <t>พื้นที่พบปะของชุมชน Young BIM สำหรับแลกเปลี่ยนความรู้ เครือข่าย และโอกาสพัฒนาทักษะดิจิทัลในวงการก่อสร้าง / A Young BIM community point for knowledge exchange, networking and digital-construction skill development.</t>
+  </si>
+  <si>
+    <t>ข้อมูลชุมชน, กิจกรรมเยาวชน/คนรุ่นใหม่, แนะแนว BIM, networking / Community information, youth and emerging-professional activities, BIM guidance and networking.</t>
+  </si>
+  <si>
+    <t>Young BIM Event Team</t>
+  </si>
+  <si>
+    <t>2 desks / 4 seats | Event-operational copy; confirm the official program, organizer contact and any membership CTA.</t>
+  </si>
+  <si>
+    <t>พื้นที่พักระหว่างกิจกรรมสำหรับผู้เข้าร่วมงาน / Rest area for attendees between sessions and booth visits.</t>
+  </si>
+  <si>
+    <t>ที่นั่งพักและจุดนัดพบ / Seating and meeting point.</t>
+  </si>
+  <si>
+    <t>Event Operations</t>
+  </si>
+  <si>
+    <t>Break area | Event-operational copy; confirm refreshments, accessibility and capacity before publishing.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="hh:mm"/>
-  </numFmts>
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -1068,7 +1392,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1083,6 +1407,7 @@
         </ext>
       </extLst>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1092,17 +1417,60 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="20">
     <dxf>
-      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="164" formatCode="hh:mm"/>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
     </dxf>
     <dxf>
       <fill>
@@ -1132,6 +1500,12 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="25" formatCode="hh:mm"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1155,8 +1529,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1174,7 +1548,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1199,8 +1573,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1218,7 +1592,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1243,8 +1617,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1287,8 +1661,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1331,8 +1705,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1375,8 +1749,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1419,8 +1793,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1463,8 +1837,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1507,8 +1881,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1551,8 +1925,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1595,8 +1969,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1639,8 +2013,8 @@
       <xdr:rowOff>94773</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>819625</xdr:rowOff>
     </xdr:to>
@@ -1683,8 +2057,8 @@
       <xdr:rowOff>81350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>833048</xdr:rowOff>
     </xdr:to>
@@ -1727,8 +2101,8 @@
       <xdr:rowOff>81350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>833048</xdr:rowOff>
     </xdr:to>
@@ -1771,8 +2145,8 @@
       <xdr:rowOff>81350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>833048</xdr:rowOff>
     </xdr:to>
@@ -1815,8 +2189,8 @@
       <xdr:rowOff>81350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>833048</xdr:rowOff>
     </xdr:to>
@@ -1859,8 +2233,8 @@
       <xdr:rowOff>81350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>833048</xdr:rowOff>
     </xdr:to>
@@ -1903,8 +2277,8 @@
       <xdr:rowOff>81350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1983739</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>358139</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>833048</xdr:rowOff>
     </xdr:to>
@@ -1964,34 +2338,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BoothsTable" displayName="BoothsTable" ref="A1:Z24" totalsRowShown="0">
-  <tableColumns count="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="BoothsTable" displayName="BoothsTable" ref="A1:U22" totalsRowShown="0">
+  <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="BoothID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Company"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Category"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Zone"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Floor"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ShortDescription"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ProductsServices"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ContactPerson"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="ContactPhone"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Website"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="QR_Link"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="LogoFile"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="X_pct"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Y_pct"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="W_pct"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="H_pct"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Visible"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="DataStatus"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Notes"/>
-    <tableColumn id="20" name="Rot_deg"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="ShortDescription" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="ProductsServices" dataDxfId="12"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="ContactPerson" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="ContactPhone" dataDxfId="10"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Website" dataDxfId="9"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="QR_Link" dataDxfId="8"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="LogoFile" dataDxfId="7"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="X_pct" dataDxfId="6"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Y_pct" dataDxfId="5"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="W_pct" dataDxfId="4"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="H_pct" dataDxfId="3"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Visible" dataDxfId="2"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="DataStatus" dataDxfId="1"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Notes" dataDxfId="0"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Rot_deg"/>
     <tableColumn id="21" name="Shape_pts"/>
-    <tableColumn id="22" name="All_X_pct"/>
-    <tableColumn id="23" name="All_Y_pct"/>
-    <tableColumn id="24" name="All_W_pct"/>
-    <tableColumn id="25" name="All_H_pct"/>
-    <tableColumn id="26" name="All_Shape_pts"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2021,8 +2390,8 @@
   <tableColumns count="19">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="ClassID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Date"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="StartTime" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="EndTime" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="StartTime" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="EndTime" dataDxfId="18"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="RoomID"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Pathway"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Topic"/>
@@ -2263,7 +2632,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="2" width="58" customWidth="1"/>
@@ -2271,111 +2640,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="3" spans="1:8" ht="16">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-    </row>
-    <row r="4" spans="1:8" ht="27.6">
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+    </row>
+    <row r="4" spans="1:8" ht="30">
       <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+    </row>
+    <row r="5" spans="1:8" ht="15">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-    </row>
-    <row r="6" spans="1:8" ht="27.6">
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
+    </row>
+    <row r="6" spans="1:8" ht="30">
       <c r="A6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-    </row>
-    <row r="7" spans="1:8" ht="27.6">
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
+    </row>
+    <row r="7" spans="1:8" ht="30">
       <c r="A7" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-    </row>
-    <row r="8" spans="1:8" ht="27.6">
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
+    </row>
+    <row r="8" spans="1:8" ht="30">
       <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" ht="27.6">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
+    </row>
+    <row r="9" spans="1:8" ht="15">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
@@ -2385,19 +2754,19 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:8" ht="15">
+      <c r="A11" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" ht="15">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -2405,7 +2774,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" ht="15">
       <c r="A13" s="2" t="s">
         <v>22</v>
       </c>
@@ -2413,7 +2782,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" ht="15">
       <c r="A14" s="2" t="s">
         <v>24</v>
       </c>
@@ -2421,7 +2790,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" ht="15">
       <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
@@ -2429,7 +2798,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" ht="15">
       <c r="A16" s="2" t="s">
         <v>28</v>
       </c>
@@ -2437,7 +2806,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" ht="15">
       <c r="A17" s="2" t="s">
         <v>30</v>
       </c>
@@ -2445,7 +2814,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" ht="15">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -2466,29 +2835,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z24"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <dimension ref="A1:U22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="15" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="28" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="11" width="24" customWidth="1"/>
-    <col min="12" max="12" width="26.69921875" customWidth="1"/>
-    <col min="13" max="17" width="9" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="19" width="28" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
-    <col min="21" max="21" width="40" customWidth="1"/>
-    <col min="22" max="25" width="10" customWidth="1"/>
-    <col min="26" max="26" width="40" customWidth="1"/>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="41.6640625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="31.6640625" style="2" customWidth="1"/>
+    <col min="11" max="11" width="8.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="6.1640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7" style="2" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.83203125" style="2" customWidth="1"/>
+    <col min="19" max="19" width="41.6640625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:21" ht="16">
       <c r="A1" s="1" t="s">
         <v>34</v>
       </c>
@@ -2546,43 +2916,16 @@
       <c r="S1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Rot_deg</t>
-        </is>
+      <c r="T1" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Shape_pts</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>All_X_pct</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>All_Y_pct</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>All_W_pct</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>All_H_pct</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>All_Shape_pts</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="2" spans="1:21" ht="90">
       <c r="A2" t="s">
         <v>53</v>
       </c>
@@ -2598,46 +2941,52 @@
       <c r="E2" t="s">
         <v>56</v>
       </c>
-      <c r="M2">
+      <c r="F2" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="M2" s="2">
         <v>43.49</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="2">
         <v>29.59</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="2">
         <v>4.49</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="2">
         <v>6.54</v>
       </c>
-      <c r="Q2" s="3" t="b">
+      <c r="Q2" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R2" t="s">
-        <v>57</v>
+      <c r="R2" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="T2">
         <v>0</v>
       </c>
-      <c r="V2">
-        <v>26.99</v>
-      </c>
-      <c r="W2">
-        <v>40.44</v>
-      </c>
-      <c r="X2">
-        <v>1.87</v>
-      </c>
-      <c r="Y2">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="3" spans="1:21" ht="75">
       <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
         <v>58</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
       </c>
       <c r="C3" t="s">
         <v>55</v>
@@ -2648,46 +2997,52 @@
       <c r="E3" t="s">
         <v>56</v>
       </c>
-      <c r="M3">
+      <c r="F3" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="M3" s="2">
         <v>48.11</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="2">
         <v>29.59</v>
       </c>
-      <c r="O3">
-        <v>4.56</v>
-      </c>
-      <c r="P3">
+      <c r="O3" s="2">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="P3" s="2">
         <v>6.54</v>
       </c>
-      <c r="Q3" s="3" t="b">
+      <c r="Q3" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R3" t="s">
-        <v>57</v>
+      <c r="R3" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="T3">
         <v>0</v>
       </c>
-      <c r="V3">
-        <v>28.87</v>
-      </c>
-      <c r="W3">
-        <v>40.44</v>
-      </c>
-      <c r="X3">
-        <v>1.95</v>
-      </c>
-      <c r="Y3">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="4" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="4" spans="1:21" ht="90">
       <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
         <v>60</v>
-      </c>
-      <c r="B4" t="s">
-        <v>61</v>
       </c>
       <c r="C4" t="s">
         <v>55</v>
@@ -2698,46 +3053,52 @@
       <c r="E4" t="s">
         <v>56</v>
       </c>
-      <c r="M4">
+      <c r="F4" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="M4" s="2">
         <v>52.86</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="2">
         <v>29.59</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="2">
         <v>4.49</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="2">
         <v>6.54</v>
       </c>
-      <c r="Q4" s="3" t="b">
+      <c r="Q4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R4" t="s">
-        <v>57</v>
+      <c r="R4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="T4">
         <v>0</v>
       </c>
-      <c r="V4">
-        <v>30.82</v>
-      </c>
-      <c r="W4">
-        <v>40.44</v>
-      </c>
-      <c r="X4">
-        <v>1.87</v>
-      </c>
-      <c r="Y4">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="5" spans="1:21" ht="75">
       <c r="A5" t="s">
+        <v>61</v>
+      </c>
+      <c r="B5" t="s">
         <v>62</v>
-      </c>
-      <c r="B5" t="s">
-        <v>63</v>
       </c>
       <c r="C5" t="s">
         <v>55</v>
@@ -2748,46 +3109,52 @@
       <c r="E5" t="s">
         <v>56</v>
       </c>
-      <c r="M5">
+      <c r="F5" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="M5" s="2">
         <v>58.72</v>
       </c>
-      <c r="N5">
+      <c r="N5" s="2">
         <v>29.59</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="2">
         <v>4.88</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="2">
         <v>6.54</v>
       </c>
-      <c r="Q5" s="3" t="b">
+      <c r="Q5" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R5" t="s">
-        <v>57</v>
+      <c r="R5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>339</v>
       </c>
       <c r="T5">
         <v>0</v>
       </c>
-      <c r="V5">
-        <v>33.96</v>
-      </c>
-      <c r="W5">
-        <v>40.44</v>
-      </c>
-      <c r="X5">
-        <v>2.06</v>
-      </c>
-      <c r="Y5">
-        <v>4.58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="6" spans="1:21" ht="90">
       <c r="A6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" t="s">
         <v>64</v>
-      </c>
-      <c r="B6" t="s">
-        <v>65</v>
       </c>
       <c r="C6" t="s">
         <v>55</v>
@@ -2798,46 +3165,52 @@
       <c r="E6" t="s">
         <v>56</v>
       </c>
-      <c r="M6">
+      <c r="F6" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="M6" s="2">
         <v>58.72</v>
       </c>
-      <c r="N6">
-        <v>36.13</v>
-      </c>
-      <c r="O6">
+      <c r="N6" s="2">
+        <v>36.130000000000003</v>
+      </c>
+      <c r="O6" s="2">
         <v>5.08</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="2">
         <v>7.52</v>
       </c>
-      <c r="Q6" s="3" t="b">
+      <c r="Q6" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R6" t="s">
-        <v>57</v>
+      <c r="R6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="T6">
         <v>0</v>
       </c>
-      <c r="V6">
-        <v>33.82</v>
-      </c>
-      <c r="W6">
-        <v>45.81</v>
-      </c>
-      <c r="X6">
-        <v>2.01</v>
-      </c>
-      <c r="Y6">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="7" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="7" spans="1:21" ht="75">
       <c r="A7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7" t="s">
         <v>66</v>
-      </c>
-      <c r="B7" t="s">
-        <v>67</v>
       </c>
       <c r="C7" t="s">
         <v>55</v>
@@ -2848,46 +3221,52 @@
       <c r="E7" t="s">
         <v>56</v>
       </c>
-      <c r="M7">
+      <c r="F7" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="M7" s="2">
         <v>52.86</v>
       </c>
-      <c r="N7">
-        <v>36.13</v>
-      </c>
-      <c r="O7">
+      <c r="N7" s="2">
+        <v>36.130000000000003</v>
+      </c>
+      <c r="O7" s="2">
         <v>4.49</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="2">
         <v>7.52</v>
       </c>
-      <c r="Q7" s="3" t="b">
+      <c r="Q7" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R7" t="s">
-        <v>57</v>
+      <c r="R7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>351</v>
       </c>
       <c r="T7">
         <v>0</v>
       </c>
-      <c r="V7">
-        <v>30.74</v>
-      </c>
-      <c r="W7">
-        <v>45.81</v>
-      </c>
-      <c r="X7">
-        <v>1.98</v>
-      </c>
-      <c r="Y7">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="8" spans="1:21" ht="75">
       <c r="A8" t="s">
+        <v>67</v>
+      </c>
+      <c r="B8" t="s">
         <v>68</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
       </c>
       <c r="C8" t="s">
         <v>55</v>
@@ -2898,46 +3277,46 @@
       <c r="E8" t="s">
         <v>56</v>
       </c>
-      <c r="M8">
+      <c r="F8" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="M8" s="2">
         <v>48.05</v>
       </c>
-      <c r="N8">
-        <v>36.13</v>
-      </c>
-      <c r="O8">
+      <c r="N8" s="2">
+        <v>36.130000000000003</v>
+      </c>
+      <c r="O8" s="2">
         <v>4.62</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="2">
         <v>7.52</v>
       </c>
-      <c r="Q8" s="3" t="b">
+      <c r="Q8" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R8" t="s">
-        <v>57</v>
+      <c r="R8" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>356</v>
       </c>
       <c r="T8">
         <v>0</v>
       </c>
-      <c r="V8">
-        <v>28.73</v>
-      </c>
-      <c r="W8">
-        <v>45.81</v>
-      </c>
-      <c r="X8">
-        <v>1.95</v>
-      </c>
-      <c r="Y8">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="9" spans="1:21" ht="90">
       <c r="A9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
       </c>
       <c r="C9" t="s">
         <v>55</v>
@@ -2948,537 +3327,580 @@
       <c r="E9" t="s">
         <v>56</v>
       </c>
-      <c r="M9">
+      <c r="F9" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="M9" s="2">
         <v>43.23</v>
       </c>
-      <c r="N9">
-        <v>36.13</v>
-      </c>
-      <c r="O9">
+      <c r="N9" s="2">
+        <v>36.130000000000003</v>
+      </c>
+      <c r="O9" s="2">
         <v>4.75</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="2">
         <v>7.52</v>
       </c>
-      <c r="Q9" s="3" t="b">
+      <c r="Q9" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R9" t="s">
-        <v>57</v>
+      <c r="R9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>362</v>
       </c>
       <c r="T9">
         <v>0</v>
       </c>
-      <c r="V9">
-        <v>26.69</v>
-      </c>
-      <c r="W9">
-        <v>45.81</v>
-      </c>
-      <c r="X9">
-        <v>1.98</v>
-      </c>
-      <c r="Y9">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="10" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="10" spans="1:21" ht="75">
       <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
         <v>72</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>73</v>
       </c>
-      <c r="C10" t="s">
-        <v>74</v>
-      </c>
       <c r="D10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
         <v>56</v>
       </c>
-      <c r="M10">
+      <c r="F10" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="M10" s="2">
         <v>35.29</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="2">
         <v>12.21</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="2">
         <v>4.82</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="2">
         <v>6.05</v>
       </c>
-      <c r="Q10" s="3" t="b">
+      <c r="Q10" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R10" t="s">
-        <v>57</v>
+      <c r="R10" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="T10">
         <v>0</v>
       </c>
-      <c r="V10">
-        <v>22.4</v>
-      </c>
-      <c r="W10">
-        <v>23.22</v>
-      </c>
-      <c r="X10">
-        <v>2.42</v>
-      </c>
-      <c r="Y10">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="11" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="11" spans="1:21" ht="75">
       <c r="A11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s">
         <v>75</v>
       </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
       <c r="C11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E11" t="s">
         <v>56</v>
       </c>
-      <c r="M11">
+      <c r="F11" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="M11" s="2">
         <v>40.1</v>
       </c>
-      <c r="N11">
+      <c r="N11" s="2">
         <v>12.21</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="2">
         <v>5.27</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="2">
         <v>6.05</v>
       </c>
-      <c r="Q11" s="3" t="b">
+      <c r="Q11" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R11" t="s">
-        <v>57</v>
+      <c r="R11" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>371</v>
       </c>
       <c r="T11">
         <v>0</v>
       </c>
-      <c r="V11">
-        <v>24.82</v>
-      </c>
-      <c r="W11">
-        <v>23.22</v>
-      </c>
-      <c r="X11">
-        <v>2.34</v>
-      </c>
-      <c r="Y11">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="12" spans="1:21" ht="75">
       <c r="A12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B12" t="s">
         <v>77</v>
       </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
       <c r="C12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
         <v>56</v>
       </c>
-      <c r="M12">
+      <c r="F12" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="M12" s="2">
         <v>45.38</v>
       </c>
-      <c r="N12">
+      <c r="N12" s="2">
         <v>12.21</v>
       </c>
-      <c r="O12">
-        <v>4.56</v>
-      </c>
-      <c r="P12">
+      <c r="O12" s="2">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="P12" s="2">
         <v>6.05</v>
       </c>
-      <c r="Q12" s="3" t="b">
+      <c r="Q12" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R12" t="s">
-        <v>57</v>
+      <c r="R12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>376</v>
       </c>
       <c r="T12">
         <v>0</v>
       </c>
-      <c r="V12">
-        <v>27.16</v>
-      </c>
-      <c r="W12">
-        <v>23.22</v>
-      </c>
-      <c r="X12">
-        <v>2.4</v>
-      </c>
-      <c r="Y12">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="13" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="13" spans="1:21" ht="75">
       <c r="A13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" t="s">
         <v>79</v>
       </c>
-      <c r="B13" t="s">
-        <v>80</v>
-      </c>
       <c r="C13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E13" t="s">
         <v>56</v>
       </c>
-      <c r="M13">
+      <c r="F13" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="M13" s="2">
         <v>49.93</v>
       </c>
-      <c r="N13">
+      <c r="N13" s="2">
         <v>12.21</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="2">
         <v>5.4</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="2">
         <v>6.05</v>
       </c>
-      <c r="Q13" s="3" t="b">
+      <c r="Q13" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R13" t="s">
-        <v>57</v>
+      <c r="R13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>382</v>
       </c>
       <c r="T13">
         <v>0</v>
       </c>
-      <c r="V13">
-        <v>29.56</v>
-      </c>
-      <c r="W13">
-        <v>23.22</v>
-      </c>
-      <c r="X13">
-        <v>2.37</v>
-      </c>
-      <c r="Y13">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="14" spans="1:21" ht="75">
       <c r="A14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B14" t="s">
         <v>81</v>
       </c>
-      <c r="B14" t="s">
-        <v>82</v>
-      </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E14" t="s">
         <v>56</v>
       </c>
-      <c r="M14">
+      <c r="F14" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="M14" s="2">
         <v>55.34</v>
       </c>
-      <c r="N14">
+      <c r="N14" s="2">
         <v>12.21</v>
       </c>
-      <c r="O14">
+      <c r="O14" s="2">
         <v>9.11</v>
       </c>
-      <c r="P14">
+      <c r="P14" s="2">
         <v>6.05</v>
       </c>
-      <c r="Q14" s="3" t="b">
+      <c r="Q14" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R14" t="s">
-        <v>57</v>
+      <c r="R14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>387</v>
       </c>
       <c r="T14">
         <v>0</v>
       </c>
-      <c r="V14">
-        <v>31.92</v>
-      </c>
-      <c r="W14">
-        <v>23.22</v>
-      </c>
-      <c r="X14">
-        <v>4.79</v>
-      </c>
-      <c r="Y14">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="15" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="15" spans="1:21" ht="90">
       <c r="A15" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
         <v>83</v>
       </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
       <c r="C15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E15" t="s">
         <v>56</v>
       </c>
-      <c r="M15">
+      <c r="F15" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="M15" s="2">
         <v>64.45</v>
       </c>
-      <c r="N15">
+      <c r="N15" s="2">
         <v>12.21</v>
       </c>
-      <c r="O15">
+      <c r="O15" s="2">
         <v>4.88</v>
       </c>
-      <c r="P15">
+      <c r="P15" s="2">
         <v>6.05</v>
       </c>
-      <c r="Q15" s="3" t="b">
+      <c r="Q15" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R15" t="s">
-        <v>57</v>
+      <c r="R15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>393</v>
       </c>
       <c r="T15">
         <v>0</v>
       </c>
-      <c r="V15">
-        <v>36.71</v>
-      </c>
-      <c r="W15">
-        <v>23.22</v>
-      </c>
-      <c r="X15">
-        <v>2.48</v>
-      </c>
-      <c r="Y15">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="16" spans="1:21" ht="75">
       <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
         <v>85</v>
       </c>
-      <c r="B16" t="s">
-        <v>86</v>
-      </c>
       <c r="C16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>56</v>
       </c>
-      <c r="M16">
+      <c r="F16" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="M16" s="2">
         <v>69.34</v>
       </c>
-      <c r="N16">
+      <c r="N16" s="2">
         <v>12.21</v>
       </c>
-      <c r="O16">
+      <c r="O16" s="2">
         <v>9.83</v>
       </c>
-      <c r="P16">
+      <c r="P16" s="2">
         <v>6.05</v>
       </c>
-      <c r="Q16" s="3" t="b">
+      <c r="Q16" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R16" t="s">
-        <v>57</v>
+      <c r="R16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>398</v>
       </c>
       <c r="T16">
         <v>0</v>
       </c>
-      <c r="V16">
-        <v>39.19</v>
-      </c>
-      <c r="W16">
-        <v>23.22</v>
-      </c>
-      <c r="X16">
-        <v>4.63</v>
-      </c>
-      <c r="Y16">
-        <v>4.87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="17" spans="1:21" ht="90">
       <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
         <v>87</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
+        <v>73</v>
+      </c>
+      <c r="D17" t="s">
         <v>88</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
-      </c>
-      <c r="D17" t="s">
-        <v>89</v>
       </c>
       <c r="E17" t="s">
         <v>56</v>
       </c>
-      <c r="M17">
+      <c r="F17" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="M17" s="2">
         <v>33.85</v>
       </c>
-      <c r="N17">
+      <c r="N17" s="2">
         <v>21.48</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="2">
         <v>3.78</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="2">
         <v>7.62</v>
       </c>
-      <c r="Q17" s="3" t="b">
+      <c r="Q17" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R17" t="s">
-        <v>57</v>
+      <c r="R17" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>404</v>
       </c>
       <c r="T17">
         <v>0</v>
       </c>
-      <c r="V17">
-        <v>22.07</v>
-      </c>
-      <c r="W17">
-        <v>32.44</v>
-      </c>
-      <c r="X17">
-        <v>1.76</v>
-      </c>
-      <c r="Y17">
-        <v>6.68</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="18" spans="1:21" ht="75">
       <c r="A18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
         <v>90</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>91</v>
       </c>
-      <c r="C18" t="s">
-        <v>92</v>
-      </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
         <v>56</v>
       </c>
-      <c r="F18" t="s">
-        <v>93</v>
-      </c>
-      <c r="M18">
+      <c r="F18" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="M18" s="2">
         <v>29.1</v>
       </c>
-      <c r="N18">
+      <c r="N18" s="2">
         <v>32.1</v>
       </c>
-      <c r="O18">
-        <v>8.53</v>
-      </c>
-      <c r="P18">
+      <c r="O18" s="2">
+        <v>8.5299999999999994</v>
+      </c>
+      <c r="P18" s="2">
         <v>6.05</v>
       </c>
-      <c r="Q18" s="3" t="b">
+      <c r="Q18" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R18" t="s">
-        <v>94</v>
-      </c>
-      <c r="S18" t="s">
-        <v>95</v>
+      <c r="R18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S18" s="2" t="s">
+        <v>408</v>
       </c>
       <c r="T18">
         <v>-18</v>
       </c>
-      <c r="V18">
-        <v>20.21</v>
-      </c>
-      <c r="W18">
-        <v>42.51</v>
-      </c>
-      <c r="X18">
-        <v>3.91</v>
-      </c>
-      <c r="Y18">
-        <v>4.72</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26" ht="72" customHeight="1">
+    </row>
+    <row r="19" spans="1:21" ht="75">
       <c r="A19" t="s">
-        <v>96</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Hardware Zone (ADVICE)</t>
-        </is>
+        <v>93</v>
+      </c>
+      <c r="B19" t="s">
+        <v>311</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E19" t="s">
         <v>56</v>
       </c>
-      <c r="F19" t="s">
-        <v>315</v>
-      </c>
-      <c r="M19">
+      <c r="F19" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="M19" s="2">
         <v>6.84</v>
       </c>
-      <c r="N19">
+      <c r="N19" s="2">
         <v>59.77</v>
       </c>
-      <c r="O19">
-        <v>34.05</v>
-      </c>
-      <c r="P19">
+      <c r="O19" s="2">
+        <v>34.049999999999997</v>
+      </c>
+      <c r="P19" s="2">
         <v>19.14</v>
       </c>
-      <c r="Q19" s="3" t="b">
+      <c r="Q19" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R19" t="s">
-        <v>57</v>
-      </c>
-      <c r="S19" t="s">
-        <v>99</v>
+      <c r="R19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>414</v>
       </c>
       <c r="T19">
         <v>0</v>
@@ -3488,340 +3910,165 @@
           <t>9.77,62.01 12.70,68.85 15.30,73.73 17.58,74.80 26.69,74.80 32.55,73.73 37.11,71.78 40.82,63.48 38.09,59.96 35.16,65.43 31.58,68.95 27.02,70.21 17.25,69.43 15.62,65.92 12.70,59.47</t>
         </is>
       </c>
-      <c r="V19">
-        <v>10.4</v>
-      </c>
-      <c r="W19">
-        <v>65.22</v>
-      </c>
-      <c r="X19">
-        <v>16.78</v>
-      </c>
-      <c r="Y19">
-        <v>16.3</v>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10.40,66.67 12.48,74.28 14.77,79.71 16.64,81.52 19.63,81.52 22.19,79.71 24.48,76.09 26.35,70.11 27.18,66.67 25.66,65.22 24.06,72.46 21.71,76.45 18.93,77.54 16.64,76.99 14.36,74.28 12.27,69.38 11.44,65.22</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" spans="1:26">
+    </row>
+    <row r="20" spans="1:21" ht="60">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B20" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D20" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="E20" t="s">
         <v>56</v>
       </c>
-      <c r="F20" t="s">
-        <v>103</v>
-      </c>
-      <c r="M20">
-        <v>33.2</v>
-      </c>
-      <c r="N20">
+      <c r="F20" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="M20" s="2">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="N20" s="2">
         <v>79.3</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="2">
         <v>15.95</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="2">
         <v>6.35</v>
       </c>
-      <c r="Q20" s="3" t="b">
+      <c r="Q20" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R20" t="s">
-        <v>94</v>
-      </c>
-      <c r="S20" t="s">
-        <v>104</v>
+      <c r="R20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>418</v>
       </c>
       <c r="T20">
         <v>0</v>
       </c>
-      <c r="V20">
-        <v>47.85</v>
-      </c>
-      <c r="W20">
-        <v>76.99</v>
-      </c>
-      <c r="X20">
-        <v>11.1</v>
-      </c>
-      <c r="Y20">
-        <v>12.68</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>YBIM</t>
-        </is>
+    </row>
+    <row r="21" spans="1:21" ht="90">
+      <c r="A21" t="s">
+        <v>312</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Young BIM Club</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Young BIM</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="M21">
+      <c r="C21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D21" t="s">
+        <v>313</v>
+      </c>
+      <c r="E21" t="s">
+        <v>56</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="M21" s="2">
         <v>18.55</v>
       </c>
-      <c r="N21">
+      <c r="N21" s="2">
         <v>43.95</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="2">
         <v>3.45</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="2">
         <v>6.45</v>
       </c>
-      <c r="Q21" s="3" t="b">
+      <c r="Q21" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Need detail</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>2 desks / 4 seats</t>
-        </is>
+      <c r="R21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>422</v>
       </c>
       <c r="T21">
         <v>0</v>
       </c>
-      <c r="V21">
-        <v>15.9</v>
-      </c>
-      <c r="W21">
-        <v>51.84</v>
-      </c>
-      <c r="X21">
+    </row>
+    <row r="22" spans="1:21" ht="45">
+      <c r="A22" t="s">
+        <v>314</v>
+      </c>
+      <c r="B22" t="s">
+        <v>315</v>
+      </c>
+      <c r="C22" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" t="s">
+        <v>315</v>
+      </c>
+      <c r="E22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="M22" s="2">
+        <v>77.86</v>
+      </c>
+      <c r="N22" s="2">
+        <v>30.47</v>
+      </c>
+      <c r="O22" s="2">
         <v>1.95</v>
       </c>
-      <c r="Y21">
-        <v>8.14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>BRK</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Break</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="M22">
-        <v>77.86</v>
-      </c>
-      <c r="N22">
-        <v>30.47</v>
-      </c>
-      <c r="O22">
-        <v>1.95</v>
-      </c>
-      <c r="P22">
+      <c r="P22" s="2">
         <v>5.86</v>
       </c>
-      <c r="Q22" s="3" t="b">
+      <c r="Q22" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Need detail</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>Break area</t>
-        </is>
+      <c r="R22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>426</v>
       </c>
       <c r="T22">
         <v>0</v>
       </c>
-      <c r="V22">
-        <v>42.77</v>
-      </c>
-      <c r="W22">
-        <v>35.71</v>
-      </c>
-      <c r="X22">
-        <v>1.21</v>
-      </c>
-      <c r="Y22">
-        <v>12.49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TR1</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Training Room 1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>1F Zone C</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Training area · 86 seats · 43 desks · speaker 1 desk + 2 seats</t>
-        </is>
-      </c>
-      <c r="Q23" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>Right-hand 1F plan (floorplan_right.png)</t>
-        </is>
-      </c>
-      <c r="T23">
-        <v>0</v>
-      </c>
-      <c r="V23">
-        <v>67.61</v>
-      </c>
-      <c r="W23">
-        <v>46.2</v>
-      </c>
-      <c r="X23">
-        <v>25.31</v>
-      </c>
-      <c r="Y23">
-        <v>22.28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>RESC</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Right escalator</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Facility</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Circulation</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1F</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Right escalator up to 2F → Training Room 2</t>
-        </is>
-      </c>
-      <c r="Q24" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Ready</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Right-hand 1F plan (floorplan_right.png)</t>
-        </is>
-      </c>
-      <c r="T24">
-        <v>0</v>
-      </c>
-      <c r="V24">
-        <v>92.93</v>
-      </c>
-      <c r="W24">
-        <v>48.55</v>
-      </c>
-      <c r="X24">
-        <v>2.64</v>
-      </c>
-      <c r="Y24">
-        <v>20.29</v>
-      </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:S50">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>$R1="Need detail"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>$R1="Ready"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3844,7 +4091,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -3856,21 +4103,21 @@
     <col min="11" max="11" width="44" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" ht="16">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>46</v>
@@ -3885,7 +4132,7 @@
         <v>49</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>52</v>
@@ -3893,91 +4140,91 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D2" t="s">
         <v>56</v>
       </c>
       <c r="E2" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="J2" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="K2" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="E3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="J3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="E4" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="J4" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="K4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D5" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="E5" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="J5" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="K5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3991,14 +4238,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S16"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="9" customWidth="1"/>
-    <col min="7" max="7" width="84.59765625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="84.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
     <col min="9" max="9" width="28" customWidth="1"/>
     <col min="10" max="10" width="62" customWidth="1"/>
@@ -4010,60 +4257,60 @@
     <col min="19" max="19" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="27.6">
+    <row r="1" spans="1:19" ht="32">
       <c r="A1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>139</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>52</v>
@@ -4071,646 +4318,646 @@
     </row>
     <row r="2" spans="1:19">
       <c r="A2" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B2" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="7">
+        <v>134</v>
+      </c>
+      <c r="C2" s="4">
         <v>0.375</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="4">
         <v>0.41666666666666669</v>
       </c>
       <c r="E2" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G2" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="H2" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="I2" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="J2" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="K2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q2" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="R2" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0.43055555555555558</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="E3" t="s">
+        <v>275</v>
+      </c>
+      <c r="F3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I3" t="s">
         <v>146</v>
       </c>
-      <c r="B3" t="s">
-        <v>141</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0.43055555555555558</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0.47222222222222221</v>
-      </c>
-      <c r="E3" t="s">
-        <v>282</v>
-      </c>
-      <c r="F3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H3" t="s">
-        <v>261</v>
-      </c>
-      <c r="I3" t="s">
-        <v>153</v>
-      </c>
       <c r="J3" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="K3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="R3" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="7">
+        <v>134</v>
+      </c>
+      <c r="C4" s="4">
         <v>0.47222222222222221</v>
       </c>
-      <c r="D4" s="7">
+      <c r="D4" s="4">
         <v>0.51388888888888884</v>
       </c>
       <c r="E4" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G4" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="H4" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="I4" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="J4" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="K4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q4" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="R4" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:19">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C5" s="7">
+        <v>134</v>
+      </c>
+      <c r="C5" s="4">
         <v>0.5625</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="4">
         <v>0.625</v>
       </c>
       <c r="E5" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="F5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G5" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="H5" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="I5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J5" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="K5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q5" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="R5" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B6" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="7">
+        <v>134</v>
+      </c>
+      <c r="C6" s="4">
         <v>0.63888888888888884</v>
       </c>
-      <c r="D6" s="7">
+      <c r="D6" s="4">
         <v>0.70138888888888884</v>
       </c>
       <c r="E6" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="F6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G6" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="H6" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="I6" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="J6" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="K6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q6" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="R6" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="B7" t="s">
-        <v>141</v>
-      </c>
-      <c r="C7" s="7">
+        <v>134</v>
+      </c>
+      <c r="C7" s="4">
         <v>0.375</v>
       </c>
-      <c r="D7" s="7">
+      <c r="D7" s="4">
         <v>0.41666666666666669</v>
       </c>
       <c r="E7" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="H7" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="I7" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="J7" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="K7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q7" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="R7" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" spans="1:19">
       <c r="A8" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="B8" t="s">
-        <v>141</v>
-      </c>
-      <c r="C8" s="7">
+        <v>134</v>
+      </c>
+      <c r="C8" s="4">
         <v>0.43055555555555558</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D8" s="4">
         <v>0.47222222222222221</v>
       </c>
       <c r="E8" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="F8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="H8" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="I8" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J8" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="K8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q8" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="R8" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:19">
       <c r="A9" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
-      </c>
-      <c r="C9" s="7">
+        <v>134</v>
+      </c>
+      <c r="C9" s="4">
         <v>0.47222222222222221</v>
       </c>
-      <c r="D9" s="7">
+      <c r="D9" s="4">
         <v>0.51388888888888884</v>
       </c>
       <c r="E9" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="F9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="H9" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="I9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="J9" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="K9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q9" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="R9" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="10" spans="1:19">
       <c r="A10" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="B10" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="7">
+        <v>134</v>
+      </c>
+      <c r="C10" s="4">
         <v>0.5625</v>
       </c>
-      <c r="D10" s="7">
+      <c r="D10" s="4">
         <v>0.625</v>
       </c>
       <c r="E10" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="F10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="H10" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="I10" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="J10" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="K10" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q10" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="R10" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C11" s="7">
+        <v>134</v>
+      </c>
+      <c r="C11" s="4">
         <v>0.63888888888888884</v>
       </c>
-      <c r="D11" s="7">
+      <c r="D11" s="4">
         <v>0.70138888888888884</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="H11" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="J11" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="K11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q11" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="R11" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C12" s="4">
+        <v>0.375</v>
+      </c>
+      <c r="D12" s="4">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E12" t="s">
+        <v>284</v>
+      </c>
+      <c r="F12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12" t="s">
+        <v>140</v>
+      </c>
+      <c r="H12" t="s">
+        <v>266</v>
+      </c>
+      <c r="I12" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="7">
-        <v>0.375</v>
-      </c>
-      <c r="D12" s="7">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="E12" t="s">
-        <v>291</v>
-      </c>
-      <c r="F12" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" t="s">
-        <v>147</v>
-      </c>
-      <c r="H12" t="s">
-        <v>273</v>
-      </c>
-      <c r="I12" t="s">
-        <v>148</v>
-      </c>
       <c r="J12" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="K12" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N12" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="O12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="P12" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="Q12" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="R12" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:19">
       <c r="A13" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s">
-        <v>141</v>
-      </c>
-      <c r="C13" s="7">
+        <v>134</v>
+      </c>
+      <c r="C13" s="4">
         <v>0.43055555555555558</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="4">
         <v>0.47222222222222221</v>
       </c>
       <c r="E13" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="F13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G13" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="H13" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="I13" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J13" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="K13" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q13" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="R13" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s">
-        <v>141</v>
-      </c>
-      <c r="C14" s="7">
+        <v>134</v>
+      </c>
+      <c r="C14" s="4">
         <v>0.47222222222222221</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="4">
         <v>0.51388888888888884</v>
       </c>
       <c r="E14" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G14" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="H14" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="I14" t="s">
         <v>54</v>
       </c>
       <c r="J14" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="K14" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N14" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="P14" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="Q14" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="R14" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="7">
+        <v>134</v>
+      </c>
+      <c r="C15" s="4">
         <v>0.5625</v>
       </c>
-      <c r="D15" s="7">
+      <c r="D15" s="4">
         <v>0.625</v>
       </c>
       <c r="E15" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="F15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G15" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="H15" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="I15" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="J15" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="K15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N15" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="O15" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="Q15" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="R15" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:19">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="7">
+        <v>134</v>
+      </c>
+      <c r="C16" s="4">
         <v>0.63888888888888884</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="4">
         <v>0.70138888888888884</v>
       </c>
       <c r="E16" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="F16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="H16" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="I16" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J16" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="K16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="Q16" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="R16" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:S100">
-    <cfRule type="expression" dxfId="3" priority="1">
+    <cfRule type="expression" dxfId="15" priority="1">
       <formula>$K1="Missing"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>$K1="Ready"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4738,7 +4985,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P12"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
@@ -4757,51 +5004,51 @@
     <col min="16" max="16" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="27.6">
+    <row r="1" spans="1:16" ht="32">
       <c r="A1" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>194</v>
       </c>
       <c r="P1" s="1" t="s">
         <v>52</v>
@@ -4809,16 +5056,16 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B2" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="D2" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E2" s="3" t="b">
         <v>1</v>
@@ -4827,33 +5074,33 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="J2" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="N2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O2" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="P2" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B3" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="E3" s="3" t="b">
         <v>1</v>
@@ -4862,33 +5109,33 @@
         <v>1</v>
       </c>
       <c r="H3" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="I3" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="J3" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="N3" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E4" s="3" t="b">
         <v>1</v>
@@ -4897,33 +5144,33 @@
         <v>1</v>
       </c>
       <c r="H4" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="I4" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="J4" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="N4" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O4" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="P4" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B5" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E5" s="3" t="b">
         <v>1</v>
@@ -4932,27 +5179,27 @@
         <v>1</v>
       </c>
       <c r="H5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="I5" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="N5" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O5" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:16">
       <c r="A6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="B6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="C6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D6" t="s">
         <v>54</v>
@@ -4964,30 +5211,30 @@
         <v>1</v>
       </c>
       <c r="H6" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J6" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="N6" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O6" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="C7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="D7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="E7" s="3" t="b">
         <v>1</v>
@@ -4996,30 +5243,30 @@
         <v>1</v>
       </c>
       <c r="H7" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="J7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="N7" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O7" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:16">
       <c r="A8" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B8" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="C8" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="D8" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E8" s="3" t="b">
         <v>1</v>
@@ -5028,24 +5275,24 @@
         <v>1</v>
       </c>
       <c r="N8" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O8" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="B9" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="C9" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D9" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E9" s="3" t="b">
         <v>1</v>
@@ -5054,30 +5301,30 @@
         <v>1</v>
       </c>
       <c r="H9" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="J9" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="N9" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O9" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="C10" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" s="3" t="b">
         <v>1</v>
@@ -5086,30 +5333,30 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="J10" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="N10" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O10" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B11" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D11" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E11" s="3" t="b">
         <v>1</v>
@@ -5118,30 +5365,30 @@
         <v>1</v>
       </c>
       <c r="H11" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="J11" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="N11" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O11" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C12" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="D12" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E12" s="3" t="b">
         <v>1</v>
@@ -5150,16 +5397,16 @@
         <v>1</v>
       </c>
       <c r="H12" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="J12" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="N12" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="O12" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
     </row>
   </sheetData>
@@ -5184,17 +5431,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="41.4">
+    <row r="1" spans="1:4" ht="48">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>36</v>
@@ -5202,13 +5449,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B2" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="D2" t="s">
         <v>55</v>
@@ -5216,56 +5463,56 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="B3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D5" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="D7" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="D8" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -5276,7 +5523,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -5284,136 +5531,136 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="21">
-      <c r="A1" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="A1" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="3" spans="1:8" ht="16">
       <c r="A3" s="1" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+        <v>240</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B4">
         <v>8</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
+      <c r="D4" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="B5">
         <v>8</v>
       </c>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B6">
         <v>3</v>
       </c>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="B7">
         <v>15</v>
       </c>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B9">
         <v>11</v>
       </c>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B10">
         <v>11</v>
       </c>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
     </row>
     <row r="12" spans="1:8">
-      <c r="A12" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
+      <c r="A12" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -5427,26 +5674,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6941e4a3-b366-4534-88af-ef700a404840">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="4ca72298-740d-4fdf-be03-dc109deea9ef" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BE0B41340E32FC43AA797B6F7BC6374D" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="e4f3dba4612ac5f682b17b5f70f3c551">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6941e4a3-b366-4534-88af-ef700a404840" xmlns:ns3="4ca72298-740d-4fdf-be03-dc109deea9ef" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db71bc9256ae1e288c085267e3887d52" ns2:_="" ns3:_="">
     <xsd:import namespace="6941e4a3-b366-4534-88af-ef700a404840"/>
@@ -5707,26 +5934,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ADB027A-59B9-4D1C-9DEC-AF4E1EE963F2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="6941e4a3-b366-4534-88af-ef700a404840"/>
-    <ds:schemaRef ds:uri="4ca72298-740d-4fdf-be03-dc109deea9ef"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63D87247-19B2-42B3-B9E0-4CF1D468167E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6941e4a3-b366-4534-88af-ef700a404840">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="4ca72298-740d-4fdf-be03-dc109deea9ef" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE06E971-C424-469B-9F02-EE92321EE105}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5743,4 +5971,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63D87247-19B2-42B3-B9E0-4CF1D468167E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9ADB027A-59B9-4D1C-9DEC-AF4E1EE963F2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="4ca72298-740d-4fdf-be03-dc109deea9ef"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6941e4a3-b366-4534-88af-ef700a404840"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>